--- a/output/pdf_financials_xlsx/SLVR.xlsx
+++ b/output/pdf_financials_xlsx/SLVR.xlsx
@@ -1362,22 +1362,22 @@
         <v>-1.306731</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.219141</v>
+        <v>-1.219141</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.370889</v>
+        <v>-0.370889</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.977175</v>
+        <v>-2.977175</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>2.720439</v>
+        <v>-2.720439</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>3.682535</v>
+        <v>-3.682535</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>3.163975</v>
+        <v>-3.163975</v>
       </c>
       <c r="Q16" s="1" t="inlineStr">
         <is>
@@ -1674,22 +1674,22 @@
         <v>-1.306731</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.219141</v>
+        <v>-1.219141</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.370889</v>
+        <v>-0.370889</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.977175</v>
+        <v>-2.977175</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>2.720439</v>
+        <v>-2.720439</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>3.682535</v>
+        <v>-3.682535</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>3.163975</v>
+        <v>-3.163975</v>
       </c>
       <c r="Q20" s="1" t="inlineStr">
         <is>
@@ -1866,22 +1866,22 @@
         <v>-1.306731</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.219141</v>
+        <v>-1.219141</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.370889</v>
+        <v>-0.370889</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.977175</v>
+        <v>-2.977175</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>2.720439</v>
+        <v>-2.720439</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>3.682535</v>
+        <v>-3.682535</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>3.163975</v>
+        <v>-3.163975</v>
       </c>
       <c r="Q23" s="1" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         </is>
       </c>
       <c r="M26" s="3" t="n">
-        <v>212.655357</v>
+        <v>-212.655357</v>
       </c>
       <c r="N26" s="1" t="inlineStr">
         <is>
@@ -2134,22 +2134,22 @@
         <v>-1.306731</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.219141</v>
+        <v>-1.219141</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.370889</v>
+        <v>-0.370889</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.977175</v>
+        <v>-2.977175</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>2.720439</v>
+        <v>-2.720439</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>3.682535</v>
+        <v>-3.682535</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>3.163975</v>
+        <v>-3.163975</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2262,22 +2262,22 @@
         <v>-1.306731</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.219141</v>
+        <v>-1.219141</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.370889</v>
+        <v>-0.370889</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.977175</v>
+        <v>-2.977175</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>2.720439</v>
+        <v>-2.720439</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>3.682535</v>
+        <v>-3.682535</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>3.163975</v>
+        <v>-3.163975</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2418,22 +2418,22 @@
         <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="1" t="inlineStr">
         <is>
@@ -6735,19 +6735,19 @@
         <v>-1.219141</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>0.370889</v>
+        <v>-0.370889</v>
       </c>
       <c r="M99" s="3" t="n">
-        <v>2.977175</v>
+        <v>-2.977175</v>
       </c>
       <c r="N99" s="3" t="n">
-        <v>2.720439</v>
+        <v>-2.720439</v>
       </c>
       <c r="O99" s="3" t="n">
-        <v>3.682535</v>
+        <v>-3.682535</v>
       </c>
       <c r="P99" s="3" t="n">
-        <v>3.163975</v>
+        <v>-3.163975</v>
       </c>
       <c r="Q99" s="1" t="inlineStr">
         <is>
@@ -24871,22 +24871,22 @@
         </is>
       </c>
       <c r="N165" s="5" t="n">
-        <v>1.219141</v>
+        <v>-1.219141</v>
       </c>
       <c r="O165" s="5" t="n">
-        <v>0.370889</v>
+        <v>-0.370889</v>
       </c>
       <c r="P165" s="5" t="n">
-        <v>2.977175</v>
+        <v>-2.977175</v>
       </c>
       <c r="Q165" s="5" t="n">
-        <v>2.720439</v>
+        <v>-2.720439</v>
       </c>
       <c r="R165" s="5" t="n">
-        <v>3.682535</v>
+        <v>-3.682535</v>
       </c>
       <c r="S165" s="5" t="n">
-        <v>3.163975</v>
+        <v>-3.163975</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -25858,10 +25858,10 @@
         </is>
       </c>
       <c r="O175" s="5" t="n">
-        <v>0.370889</v>
+        <v>-0.370889</v>
       </c>
       <c r="P175" s="5" t="n">
-        <v>2.977175</v>
+        <v>-2.977175</v>
       </c>
       <c r="Q175" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SLVR.xlsx
+++ b/output/pdf_financials_xlsx/SLVR.xlsx
@@ -1091,19 +1091,19 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.007735</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008488000000000001</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002246</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.01988</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.012428</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -1112,16 +1112,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.026266</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.057251</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.520954</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.78704</v>
       </c>
       <c r="Q12" s="1" t="inlineStr">
         <is>
@@ -2119,19 +2119,19 @@
         <v>-0.640882</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-1.910207</v>
+        <v>-1.917942</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.372574</v>
+        <v>-1.381062</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.833549</v>
+        <v>-1.835795</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-10.166843</v>
+        <v>-10.186723</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.306731</v>
+        <v>-1.319159</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-1.219141</v>
@@ -2140,16 +2140,16 @@
         <v>-0.370889</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.977175</v>
+        <v>-2.950909</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-2.720439</v>
+        <v>-2.663188</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-3.682535</v>
+        <v>-3.161581</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.163975</v>
+        <v>-2.376935</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2247,19 +2247,19 @@
         <v>-0.640882</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-1.910207</v>
+        <v>-1.917942</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.372574</v>
+        <v>-1.381062</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.833549</v>
+        <v>-1.835795</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-10.166843</v>
+        <v>-10.186723</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.306731</v>
+        <v>-1.319159</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>-1.219141</v>
@@ -2268,16 +2268,16 @@
         <v>-0.370889</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.977175</v>
+        <v>-2.950909</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-2.720439</v>
+        <v>-2.663188</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-3.682535</v>
+        <v>-3.161581</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.163975</v>
+        <v>-2.376935</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.648628</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.228999</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>1.955207</v>
@@ -2581,28 +2581,28 @@
         <v>0.017844</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.022364</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.089438</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>25.935925</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>33.620351</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>29.80366</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>9.223376</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>3.191662</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>117.059288</v>
       </c>
     </row>
     <row r="35">
@@ -2677,10 +2677,10 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.648628</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.228999</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>1.955207</v>
@@ -2701,28 +2701,28 @@
         <v>0.017844</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.022364</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.089438</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>25.935925</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>33.620351</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>29.80366</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>9.223376</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>3.191662</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>117.059288</v>
       </c>
     </row>
     <row r="37">
@@ -3397,10 +3397,10 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.678186</v>
+        <v>0.029558</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.296377</v>
+        <v>0.06737799999999999</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.032169</v>
@@ -3421,28 +3421,28 @@
         <v>0.081721</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.107185</v>
+        <v>0.08482099999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.147867</v>
+        <v>0.058429</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>26.286142</v>
+        <v>0.350217</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>33.760969</v>
+        <v>0.140618</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>30.157927</v>
+        <v>0.354267</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>10.649873</v>
+        <v>1.426497</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>3.585126</v>
+        <v>0.393464</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>117.461274</v>
+        <v>0.401986</v>
       </c>
     </row>
     <row r="49">
@@ -9117,7 +9117,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24521,7 +24521,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -27907,7 +27907,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -29083,7 +29083,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">

--- a/output/pdf_financials_xlsx/SLVR.xlsx
+++ b/output/pdf_financials_xlsx/SLVR.xlsx
@@ -631,10 +631,8 @@
       <c r="B5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="3" t="n">
         <v>0</v>
@@ -759,10 +757,8 @@
       <c r="B7" s="3" t="n">
         <v>0.005109</v>
       </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>0.048332</v>
@@ -823,10 +819,8 @@
       <c r="B8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>0</v>
@@ -887,10 +881,8 @@
       <c r="B9" s="3" t="n">
         <v>0.00013</v>
       </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>0.017449</v>
@@ -951,10 +943,8 @@
       <c r="B10" s="3" t="n">
         <v>0.005239</v>
       </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.06578100000000001</v>
@@ -1079,10 +1069,8 @@
       <c r="B12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -1143,10 +1131,8 @@
       <c r="B13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>-0</v>
@@ -1207,10 +1193,8 @@
       <c r="B14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>0</v>
@@ -1271,10 +1255,8 @@
       <c r="B15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>0</v>
@@ -1335,10 +1317,8 @@
       <c r="B16" s="3" t="n">
         <v>-0.154853</v>
       </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C16" s="3" t="n">
+        <v>-0.154853</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.631835</v>
@@ -1399,10 +1379,8 @@
       <c r="B17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-0.0315</v>
@@ -1647,10 +1625,8 @@
       <c r="B20" s="3" t="n">
         <v>-0.154853</v>
       </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C20" s="3" t="n">
+        <v>-0.154853</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.600335</v>
@@ -1711,10 +1687,8 @@
       <c r="B21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -1775,10 +1749,8 @@
       <c r="B22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>0</v>
@@ -1839,10 +1811,8 @@
       <c r="B23" s="3" t="n">
         <v>-0.154853</v>
       </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C23" s="3" t="n">
+        <v>-0.154853</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.600335</v>
@@ -1903,10 +1873,8 @@
       <c r="B24" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C24" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -1967,10 +1935,8 @@
       <c r="B25" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C25" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>-0.07000000000000001</v>
@@ -2031,10 +1997,8 @@
       <c r="B26" s="3" t="n">
         <v>3.871325</v>
       </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C26" s="3" t="n">
+        <v>7.74265</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>8.576214</v>
@@ -2107,10 +2071,8 @@
       <c r="B27" s="3" t="n">
         <v>-0.154853</v>
       </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C27" s="3" t="n">
+        <v>-0.154853</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.631835</v>
@@ -2171,10 +2133,8 @@
       <c r="B28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>0</v>
@@ -2235,10 +2195,8 @@
       <c r="B29" s="3" t="n">
         <v>-0.154853</v>
       </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C29" s="3" t="n">
+        <v>-0.154853</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.631835</v>
@@ -2391,10 +2349,8 @@
       <c r="B31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-4.985478803801626</v>
@@ -4453,22 +4409,22 @@
         </is>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.021349</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.049595</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.060611</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.053276</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>0.258965</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.475367</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0</v>
@@ -4483,22 +4439,22 @@
         <v>0</v>
       </c>
       <c r="M64" s="3" t="n">
-        <v>0</v>
+        <v>1.915563</v>
       </c>
       <c r="N64" s="3" t="n">
-        <v>0</v>
+        <v>3.707454</v>
       </c>
       <c r="O64" s="3" t="n">
-        <v>0</v>
+        <v>2.665633</v>
       </c>
       <c r="P64" s="3" t="n">
-        <v>0</v>
+        <v>1.373964</v>
       </c>
       <c r="Q64" s="3" t="n">
-        <v>0</v>
+        <v>0.7651289999999999</v>
       </c>
       <c r="R64" s="3" t="n">
-        <v>0</v>
+        <v>1.070215</v>
       </c>
     </row>
     <row r="65">
@@ -4633,52 +4589,52 @@
         </is>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.028931</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.187694</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.122984</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.143912</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.172643</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.09268999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.14019</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.245482</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.09367200000000001</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.17967</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.09867099999999999</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.178</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.13652</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.284454</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>0</v>
+        <v>0.161954</v>
       </c>
     </row>
     <row r="68">
@@ -6705,10 +6661,8 @@
       <c r="B99" s="3" t="n">
         <v>-0.154853</v>
       </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C99" s="3" t="n">
+        <v>-0.154853</v>
       </c>
       <c r="D99" s="3" t="n">
         <v>-0.600335</v>
@@ -6769,10 +6723,8 @@
       <c r="B100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="3" t="n">
         <v>0</v>
@@ -6829,10 +6781,8 @@
       <c r="B101" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="3" t="n">
         <v>0</v>
@@ -6889,10 +6839,8 @@
       <c r="B102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="3" t="n">
         <v>0</v>
@@ -6949,10 +6897,8 @@
       <c r="B103" s="3" t="n">
         <v>-0.011623</v>
       </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C103" s="3" t="n">
+        <v>-0.011623</v>
       </c>
       <c r="D103" s="3" t="n">
         <v>-0.004689</v>
@@ -7009,10 +6955,8 @@
       <c r="B104" s="3" t="n">
         <v>0.026349</v>
       </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C104" s="3" t="n">
+        <v>0.026349</v>
       </c>
       <c r="D104" s="3" t="n">
         <v>0.029096</v>
@@ -7069,10 +7013,8 @@
       <c r="B105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="3" t="n">
         <v>0</v>
@@ -7129,10 +7071,8 @@
       <c r="B106" s="3" t="n">
         <v>0.014726</v>
       </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C106" s="3" t="n">
+        <v>0.014726</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.024407</v>
@@ -7189,10 +7129,8 @@
       <c r="B107" s="3" t="n">
         <v>0.094</v>
       </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C107" s="3" t="n">
+        <v>0.094</v>
       </c>
       <c r="D107" s="3" t="n">
         <v>0</v>
@@ -7249,10 +7187,8 @@
       <c r="B108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="3" t="n">
         <v>0</v>
@@ -7309,10 +7245,8 @@
       <c r="B109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="3" t="n">
         <v>0</v>
@@ -7369,10 +7303,8 @@
       <c r="B110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -7429,10 +7361,8 @@
       <c r="B111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -7489,10 +7419,8 @@
       <c r="B112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="3" t="n">
         <v>0</v>
@@ -7549,10 +7477,8 @@
       <c r="B113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="3" t="n">
         <v>0</v>
@@ -7609,10 +7535,8 @@
       <c r="B114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="3" t="n">
         <v>0</v>
@@ -7669,10 +7593,8 @@
       <c r="B115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -7729,10 +7651,8 @@
       <c r="B116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="3" t="n">
         <v>0</v>
@@ -7789,10 +7709,8 @@
       <c r="B117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="3" t="n">
         <v>0</v>
@@ -7849,10 +7767,8 @@
       <c r="B118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0</v>
@@ -7979,10 +7895,8 @@
       <c r="B120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="3" t="n">
         <v>0</v>
@@ -8039,10 +7953,8 @@
       <c r="B121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -8099,10 +8011,8 @@
       <c r="B122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="3" t="n">
         <v>0</v>
@@ -8159,10 +8069,8 @@
       <c r="B123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="3" t="n">
         <v>0</v>
@@ -8219,10 +8127,8 @@
       <c r="B124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -8279,10 +8185,8 @@
       <c r="B125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -8339,10 +8243,8 @@
       <c r="B126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="3" t="n">
         <v>0</v>
@@ -8491,10 +8393,8 @@
       <c r="B128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="3" t="n">
         <v>0</v>
@@ -8611,10 +8511,8 @@
       <c r="B130" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C130" s="3" t="n">
+        <v>0.648628</v>
       </c>
       <c r="D130" s="3" t="n">
         <v>0.648628</v>
@@ -8671,10 +8569,8 @@
       <c r="B131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="3" t="n">
         <v>0</v>
@@ -8731,10 +8627,8 @@
       <c r="B132" s="3" t="n">
         <v>0.648628</v>
       </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C132" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D132" s="3" t="n">
         <v>-0.419629</v>
@@ -8791,10 +8685,8 @@
       <c r="B133" s="3" t="n">
         <v>0.648628</v>
       </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C133" s="3" t="n">
+        <v>0.648628</v>
       </c>
       <c r="D133" s="3" t="n">
         <v>0.228999</v>
@@ -8851,10 +8743,8 @@
       <c r="B134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -8983,7 +8873,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U226"/>
+  <dimension ref="A1:U236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -19063,10 +18953,8 @@
       <c r="E104" s="5" t="n">
         <v>0.85</v>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F104" s="5" t="n">
+        <v>0.71269</v>
       </c>
       <c r="G104" s="5" t="n">
         <v>0.505</v>
@@ -23571,22 +23459,22 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Consulting fees (note 10)</t>
+          <t>Net loss for the period</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -23594,10 +23482,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F151" s="5" t="n">
+        <v>-0.154853</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -23654,11 +23540,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R151" s="5" t="n">
-        <v>0.8573</v>
-      </c>
-      <c r="S151" s="5" t="n">
-        <v>0.845</v>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -23674,22 +23564,22 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Charges to loss not affecting cash</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Stock-based compensation expenses</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -23697,10 +23587,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F152" s="5" t="n">
+        <v>0.094</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -23742,20 +23630,30 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O152" s="5" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="P152" s="5" t="n">
-        <v>0.0308</v>
-      </c>
-      <c r="Q152" s="5" t="n">
-        <v>0.0152</v>
-      </c>
-      <c r="R152" s="5" t="n">
-        <v>0.001194</v>
-      </c>
-      <c r="S152" s="5" t="n">
-        <v>0.002079</v>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -23771,66 +23669,92 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Charges to loss not affecting cash</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Dues and fees</t>
+          <t>Charges to loss not affecting cash total</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
-      <c r="E153" s="5" t="n">
-        <v>0.009558000000000001</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="n">
-        <v>0.031997</v>
-      </c>
-      <c r="H153" s="5" t="n">
-        <v>0.021012</v>
-      </c>
-      <c r="I153" s="5" t="n">
-        <v>0.034714</v>
-      </c>
-      <c r="J153" s="5" t="n">
-        <v>0.030686</v>
-      </c>
-      <c r="K153" s="5" t="n">
-        <v>0.055568</v>
-      </c>
-      <c r="L153" s="5" t="n">
-        <v>0.102579</v>
-      </c>
-      <c r="M153" s="5" t="n">
-        <v>0.047517</v>
-      </c>
-      <c r="N153" s="5" t="n">
-        <v>0.042864</v>
-      </c>
-      <c r="O153" s="5" t="n">
-        <v>0.070659</v>
-      </c>
-      <c r="P153" s="5" t="n">
-        <v>0.106622</v>
-      </c>
-      <c r="Q153" s="5" t="n">
-        <v>0.166637</v>
-      </c>
-      <c r="R153" s="5" t="n">
-        <v>0.06743399999999999</v>
-      </c>
-      <c r="S153" s="5" t="n">
-        <v>0.041273</v>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F153" s="5" t="n">
+        <v>-0.060853</v>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -23846,70 +23770,92 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Charges to loss not affecting cash</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E154" s="5" t="n">
-        <v>0.002378</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="n">
-        <v>0.0202</v>
-      </c>
-      <c r="H154" s="5" t="n">
-        <v>0.024552</v>
-      </c>
-      <c r="I154" s="5" t="n">
-        <v>0.0431</v>
-      </c>
-      <c r="J154" s="5" t="n">
-        <v>0.046705</v>
-      </c>
-      <c r="K154" s="5" t="n">
-        <v>0.090494</v>
-      </c>
-      <c r="L154" s="5" t="n">
-        <v>0.020575</v>
-      </c>
-      <c r="M154" s="5" t="n">
-        <v>0.048605</v>
-      </c>
-      <c r="N154" s="5" t="n">
-        <v>0.06717099999999999</v>
-      </c>
-      <c r="O154" s="5" t="n">
-        <v>0.080651</v>
-      </c>
-      <c r="P154" s="5" t="n">
-        <v>0.103338</v>
-      </c>
-      <c r="Q154" s="5" t="n">
-        <v>0.177243</v>
-      </c>
-      <c r="R154" s="5" t="n">
-        <v>0.160167</v>
-      </c>
-      <c r="S154" s="5" t="n">
-        <v>0.175613</v>
+          <t>Increase in sales tax recoverable</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F154" s="5" t="n">
+        <v>-0.017935</v>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T154" t="inlineStr">
         <is>
@@ -23925,29 +23871,31 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Charges to loss not affecting cash</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Office and other</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
+          <t>Increase in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F155" s="5" t="n">
+        <v>0.026349</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -23964,35 +23912,55 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J155" s="5" t="n">
-        <v>0.035258</v>
-      </c>
-      <c r="K155" s="5" t="n">
-        <v>0.046331</v>
-      </c>
-      <c r="L155" s="5" t="n">
-        <v>0.142301</v>
-      </c>
-      <c r="M155" s="5" t="n">
-        <v>0.115222</v>
-      </c>
-      <c r="N155" s="5" t="n">
-        <v>0.115855</v>
-      </c>
-      <c r="O155" s="5" t="n">
-        <v>0.079939</v>
-      </c>
-      <c r="P155" s="5" t="n">
-        <v>0.089362</v>
-      </c>
-      <c r="Q155" s="5" t="n">
-        <v>0.244125</v>
-      </c>
-      <c r="R155" s="5" t="n">
-        <v>0.282532</v>
-      </c>
-      <c r="S155" s="5" t="n">
-        <v>0.105581</v>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -24008,70 +23976,96 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Charges to loss not affecting cash</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Increase in prepaid expenses</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E156" s="5" t="n">
-        <v>0.040976</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="n">
-        <v>0.181317</v>
-      </c>
-      <c r="H156" s="5" t="n">
-        <v>0.099662</v>
-      </c>
-      <c r="I156" s="5" t="n">
-        <v>0.244752</v>
-      </c>
-      <c r="J156" s="5" t="n">
-        <v>0.296095</v>
-      </c>
-      <c r="K156" s="5" t="n">
-        <v>0.17194</v>
-      </c>
-      <c r="L156" s="5" t="n">
-        <v>0.118919</v>
-      </c>
-      <c r="M156" s="5" t="n">
-        <v>0.07768600000000001</v>
-      </c>
-      <c r="N156" s="5" t="n">
-        <v>0.064794</v>
-      </c>
-      <c r="O156" s="5" t="n">
-        <v>0.039086</v>
-      </c>
-      <c r="P156" s="5" t="n">
-        <v>0.204082</v>
-      </c>
-      <c r="Q156" s="5" t="n">
-        <v>0.193813</v>
-      </c>
-      <c r="R156" s="5" t="n">
-        <v>0.223665</v>
-      </c>
-      <c r="S156" s="5" t="n">
-        <v>0.183517</v>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F156" s="5" t="n">
+        <v>-0.011623</v>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -24087,22 +24081,22 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Shareholder communication</t>
+          <t>Net change in cash for the period and Cash – End of period</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -24110,49 +24104,73 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G157" s="5" t="n">
-        <v>0.011562</v>
-      </c>
-      <c r="H157" s="5" t="n">
-        <v>0.033087</v>
-      </c>
-      <c r="I157" s="5" t="n">
-        <v>0.057477</v>
-      </c>
-      <c r="J157" s="5" t="n">
-        <v>0.038729</v>
-      </c>
-      <c r="K157" s="5" t="n">
-        <v>0.045586</v>
-      </c>
-      <c r="L157" s="5" t="n">
-        <v>0.129128</v>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v>0.172852</v>
-      </c>
-      <c r="N157" s="5" t="n">
-        <v>0.073105</v>
-      </c>
-      <c r="O157" s="5" t="n">
-        <v>0.07587000000000001</v>
-      </c>
-      <c r="P157" s="5" t="n">
-        <v>0.166824</v>
-      </c>
-      <c r="Q157" s="5" t="n">
-        <v>0.326814</v>
-      </c>
-      <c r="R157" s="5" t="n">
-        <v>0.238351</v>
-      </c>
-      <c r="S157" s="5" t="n">
-        <v>0.451473</v>
+      <c r="F157" s="5" t="n">
+        <v>0.648628</v>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -24178,10 +24196,14 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 11)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
+          <t>Consulting fees (note 10)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -24248,10 +24270,10 @@
         </is>
       </c>
       <c r="R158" s="5" t="n">
-        <v>2.022</v>
+        <v>0.8573</v>
       </c>
       <c r="S158" s="5" t="n">
-        <v>1.74</v>
+        <v>0.845</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -24277,60 +24299,78 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E159" s="5" t="n">
-        <v>0.002731</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G159" s="5" t="n">
-        <v>0.01657</v>
-      </c>
-      <c r="H159" s="5" t="n">
-        <v>0.009717999999999999</v>
-      </c>
-      <c r="I159" s="5" t="n">
-        <v>0.040466</v>
-      </c>
-      <c r="J159" s="5" t="n">
-        <v>0.055866</v>
-      </c>
-      <c r="K159" s="5" t="n">
-        <v>0.044906</v>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v>0.104063</v>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v>0.104157</v>
-      </c>
-      <c r="N159" s="5" t="n">
-        <v>0.025268</v>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O159" s="5" t="n">
-        <v>0.049033</v>
+        <v>0.031</v>
       </c>
       <c r="P159" s="5" t="n">
-        <v>0.011499</v>
+        <v>0.0308</v>
       </c>
       <c r="Q159" s="5" t="n">
-        <v>0.115032</v>
+        <v>0.0152</v>
       </c>
       <c r="R159" s="5" t="n">
-        <v>0.120791</v>
+        <v>0.001194</v>
       </c>
       <c r="S159" s="5" t="n">
-        <v>0.146752</v>
+        <v>0.002079</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -24356,14 +24396,12 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
+          <t>Dues and fees</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E160" s="5" t="n">
+        <v>0.009558000000000001</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -24371,43 +24409,43 @@
         </is>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.089408</v>
+        <v>0.031997</v>
       </c>
       <c r="H160" s="5" t="n">
-        <v>0.231974</v>
+        <v>0.021012</v>
       </c>
       <c r="I160" s="5" t="n">
-        <v>0.228957</v>
+        <v>0.034714</v>
       </c>
       <c r="J160" s="5" t="n">
-        <v>0.219362</v>
+        <v>0.030686</v>
       </c>
       <c r="K160" s="5" t="n">
-        <v>0.267848</v>
+        <v>0.055568</v>
       </c>
       <c r="L160" s="5" t="n">
-        <v>0.059458</v>
+        <v>0.102579</v>
       </c>
       <c r="M160" s="5" t="n">
-        <v>0.145716</v>
+        <v>0.047517</v>
       </c>
       <c r="N160" s="5" t="n">
-        <v>0.13589</v>
+        <v>0.042864</v>
       </c>
       <c r="O160" s="5" t="n">
-        <v>0.06551999999999999</v>
+        <v>0.070659</v>
       </c>
       <c r="P160" s="5" t="n">
-        <v>0.127951</v>
+        <v>0.106622</v>
       </c>
       <c r="Q160" s="5" t="n">
-        <v>0.130917</v>
+        <v>0.166637</v>
       </c>
       <c r="R160" s="5" t="n">
-        <v>0.173566</v>
+        <v>0.06743399999999999</v>
       </c>
       <c r="S160" s="5" t="n">
-        <v>0.182124</v>
+        <v>0.041273</v>
       </c>
       <c r="T160" t="inlineStr">
         <is>
@@ -24433,64 +24471,60 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Operating expenses total</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E161" s="5" t="n">
+        <v>0.002378</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G161" s="5" t="n">
+        <v>0.0202</v>
       </c>
       <c r="H161" s="5" t="n">
-        <v>0.640882</v>
+        <v>0.024552</v>
       </c>
       <c r="I161" s="5" t="n">
-        <v>1.917942</v>
+        <v>0.0431</v>
       </c>
       <c r="J161" s="5" t="n">
-        <v>1.381062</v>
+        <v>0.046705</v>
       </c>
       <c r="K161" s="5" t="n">
-        <v>1.835795</v>
+        <v>0.090494</v>
       </c>
       <c r="L161" s="5" t="n">
-        <v>10.186723</v>
+        <v>0.020575</v>
       </c>
       <c r="M161" s="5" t="n">
-        <v>1.319159</v>
+        <v>0.048605</v>
       </c>
       <c r="N161" s="5" t="n">
-        <v>1.219141</v>
+        <v>0.06717099999999999</v>
       </c>
       <c r="O161" s="5" t="n">
-        <v>0.946453</v>
+        <v>0.080651</v>
       </c>
       <c r="P161" s="5" t="n">
-        <v>2.280959</v>
+        <v>0.103338</v>
       </c>
       <c r="Q161" s="5" t="n">
-        <v>2.805105</v>
+        <v>0.177243</v>
       </c>
       <c r="R161" s="5" t="n">
-        <v>4.147</v>
+        <v>0.160167</v>
       </c>
       <c r="S161" s="5" t="n">
-        <v>3.873412</v>
+        <v>0.175613</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -24511,19 +24545,15 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Office and other</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -24549,47 +24579,35 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J162" s="5" t="n">
+        <v>0.035258</v>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>0.046331</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>0.142301</v>
+      </c>
+      <c r="M162" s="5" t="n">
+        <v>0.115222</v>
+      </c>
+      <c r="N162" s="5" t="n">
+        <v>0.115855</v>
+      </c>
+      <c r="O162" s="5" t="n">
+        <v>0.079939</v>
       </c>
       <c r="P162" s="5" t="n">
-        <v>-0.026266</v>
+        <v>0.089362</v>
       </c>
       <c r="Q162" s="5" t="n">
-        <v>-0.057251</v>
+        <v>0.244125</v>
       </c>
       <c r="R162" s="5" t="n">
-        <v>-0.520954</v>
+        <v>0.282532</v>
       </c>
       <c r="S162" s="5" t="n">
-        <v>-0.78704</v>
+        <v>0.105581</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -24610,89 +24628,63 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E163" s="5" t="n">
+        <v>0.040976</v>
+      </c>
+      <c r="F163" s="5" t="n">
+        <v>0.040976</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.181317</v>
+      </c>
+      <c r="H163" s="5" t="n">
+        <v>0.099662</v>
+      </c>
+      <c r="I163" s="5" t="n">
+        <v>0.244752</v>
+      </c>
+      <c r="J163" s="5" t="n">
+        <v>0.296095</v>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>0.17194</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>0.118919</v>
+      </c>
+      <c r="M163" s="5" t="n">
+        <v>0.07768600000000001</v>
+      </c>
+      <c r="N163" s="5" t="n">
+        <v>0.064794</v>
+      </c>
+      <c r="O163" s="5" t="n">
+        <v>0.039086</v>
+      </c>
+      <c r="P163" s="5" t="n">
+        <v>0.204082</v>
+      </c>
+      <c r="Q163" s="5" t="n">
+        <v>0.193813</v>
       </c>
       <c r="R163" s="5" t="n">
-        <v>0.056489</v>
+        <v>0.223665</v>
       </c>
       <c r="S163" s="5" t="n">
-        <v>0.07760300000000001</v>
+        <v>0.183517</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -24713,15 +24705,19 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Other expenses (income) total</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Shareholder communication</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -24732,66 +24728,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G164" s="5" t="n">
+        <v>0.011562</v>
+      </c>
+      <c r="H164" s="5" t="n">
+        <v>0.033087</v>
+      </c>
+      <c r="I164" s="5" t="n">
+        <v>0.057477</v>
+      </c>
+      <c r="J164" s="5" t="n">
+        <v>0.038729</v>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>0.045586</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>0.129128</v>
+      </c>
+      <c r="M164" s="5" t="n">
+        <v>0.172852</v>
+      </c>
+      <c r="N164" s="5" t="n">
+        <v>0.073105</v>
+      </c>
+      <c r="O164" s="5" t="n">
+        <v>0.07587000000000001</v>
+      </c>
+      <c r="P164" s="5" t="n">
+        <v>0.166824</v>
+      </c>
+      <c r="Q164" s="5" t="n">
+        <v>0.326814</v>
       </c>
       <c r="R164" s="5" t="n">
-        <v>-0.464465</v>
+        <v>0.238351</v>
       </c>
       <c r="S164" s="5" t="n">
-        <v>-0.709437</v>
+        <v>0.451473</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -24812,19 +24786,15 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the years</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (note 11)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -24870,23 +24840,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N165" s="5" t="n">
-        <v>-1.219141</v>
-      </c>
-      <c r="O165" s="5" t="n">
-        <v>-0.370889</v>
-      </c>
-      <c r="P165" s="5" t="n">
-        <v>-2.977175</v>
-      </c>
-      <c r="Q165" s="5" t="n">
-        <v>-2.720439</v>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R165" s="5" t="n">
-        <v>-3.682535</v>
+        <v>2.022</v>
       </c>
       <c r="S165" s="5" t="n">
-        <v>-3.163975</v>
+        <v>1.74</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -24907,81 +24885,65 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Loss per share – Basic and diluted</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E166" s="5" t="n">
+        <v>0.002731</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G166" s="5" t="n">
+        <v>0.01657</v>
+      </c>
+      <c r="H166" s="5" t="n">
+        <v>0.009717999999999999</v>
+      </c>
+      <c r="I166" s="5" t="n">
+        <v>0.040466</v>
+      </c>
+      <c r="J166" s="5" t="n">
+        <v>0.055866</v>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>0.044906</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>0.104063</v>
+      </c>
+      <c r="M166" s="5" t="n">
+        <v>0.104157</v>
       </c>
       <c r="N166" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.025268</v>
       </c>
       <c r="O166" s="5" t="n">
-        <v>-2e-09</v>
+        <v>0.049033</v>
       </c>
       <c r="P166" s="5" t="n">
-        <v>1.4e-08</v>
+        <v>0.011499</v>
       </c>
       <c r="Q166" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.115032</v>
       </c>
       <c r="R166" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.120791</v>
       </c>
       <c r="S166" s="5" t="n">
-        <v>1e-08</v>
+        <v>0.146752</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -25002,12 +24964,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Weighted average outstanding common shares – Basic and</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Weighted average outstanding common shares – Basic and diluted</t>
+          <t>Wages and benefits</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
@@ -25021,58 +24983,44 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G167" s="5" t="n">
+        <v>0.089408</v>
+      </c>
+      <c r="H167" s="5" t="n">
+        <v>0.231974</v>
+      </c>
+      <c r="I167" s="5" t="n">
+        <v>0.228957</v>
+      </c>
+      <c r="J167" s="5" t="n">
+        <v>0.219362</v>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>0.267848</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>0.059458</v>
+      </c>
+      <c r="M167" s="5" t="n">
+        <v>0.145716</v>
       </c>
       <c r="N167" s="5" t="n">
-        <v>140.859109</v>
+        <v>0.13589</v>
       </c>
       <c r="O167" s="5" t="n">
-        <v>151.788479</v>
+        <v>0.06551999999999999</v>
       </c>
       <c r="P167" s="5" t="n">
-        <v>206.411561</v>
+        <v>0.127951</v>
       </c>
       <c r="Q167" s="5" t="n">
-        <v>263.547976</v>
+        <v>0.130917</v>
       </c>
       <c r="R167" s="5" t="n">
-        <v>311.783728</v>
+        <v>0.173566</v>
       </c>
       <c r="S167" s="5" t="n">
-        <v>364.884309</v>
+        <v>0.182124</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -25098,12 +25046,12 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Consulting fees (note 9)</t>
+          <t>Operating expenses total</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -25121,59 +25069,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H168" s="5" t="n">
+        <v>0.640882</v>
+      </c>
+      <c r="I168" s="5" t="n">
+        <v>1.917942</v>
+      </c>
+      <c r="J168" s="5" t="n">
+        <v>1.381062</v>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>1.835795</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>10.186723</v>
+      </c>
+      <c r="M168" s="5" t="n">
+        <v>1.319159</v>
+      </c>
+      <c r="N168" s="5" t="n">
+        <v>1.219141</v>
       </c>
       <c r="O168" s="5" t="n">
-        <v>0.411695</v>
+        <v>0.946453</v>
       </c>
       <c r="P168" s="5" t="n">
-        <v>0.687481</v>
+        <v>2.280959</v>
       </c>
       <c r="Q168" s="5" t="n">
-        <v>0.773324</v>
-      </c>
-      <c r="R168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2.805105</v>
+      </c>
+      <c r="R168" s="5" t="n">
+        <v>4.147</v>
+      </c>
+      <c r="S168" s="5" t="n">
+        <v>3.873412</v>
       </c>
       <c r="T168" t="inlineStr">
         <is>
@@ -25194,15 +25124,19 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Stock-based compensation (note 10)</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -25253,24 +25187,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O169" s="5" t="n">
-        <v>0.043</v>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P169" s="5" t="n">
-        <v>0.753</v>
+        <v>-0.026266</v>
       </c>
       <c r="Q169" s="5" t="n">
-        <v>0.662</v>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.057251</v>
+      </c>
+      <c r="R169" s="5" t="n">
+        <v>-0.520954</v>
+      </c>
+      <c r="S169" s="5" t="n">
+        <v>-0.78704</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -25296,7 +25228,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain) (note 3)</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -25354,24 +25286,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O170" s="5" t="n">
-        <v>-0.261635</v>
-      </c>
-      <c r="P170" s="5" t="n">
-        <v>0.020592</v>
-      </c>
-      <c r="Q170" s="5" t="n">
-        <v>-0.027415</v>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R170" s="5" t="n">
+        <v>0.056489</v>
+      </c>
+      <c r="S170" s="5" t="n">
+        <v>0.07760300000000001</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -25397,7 +25331,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Government assistance benefit (note 8)</t>
+          <t>Other expenses (income) total</t>
         </is>
       </c>
       <c r="D171" t="inlineStr"/>
@@ -25456,23 +25390,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P171" s="5" t="n">
-        <v>-0.017</v>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="R171" s="5" t="n">
+        <v>-0.464465</v>
+      </c>
+      <c r="S171" s="5" t="n">
+        <v>-0.709437</v>
       </c>
       <c r="T171" t="inlineStr">
         <is>
@@ -25498,10 +25430,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Loss on settlement of accounts payable (note 10)</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the years</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -25547,33 +25483,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N172" s="5" t="n">
+        <v>-1.219141</v>
+      </c>
+      <c r="O172" s="5" t="n">
+        <v>-0.370889</v>
       </c>
       <c r="P172" s="5" t="n">
-        <v>0.71889</v>
-      </c>
-      <c r="Q172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.977175</v>
+      </c>
+      <c r="Q172" s="5" t="n">
+        <v>-2.720439</v>
+      </c>
+      <c r="R172" s="5" t="n">
+        <v>-3.682535</v>
+      </c>
+      <c r="S172" s="5" t="n">
+        <v>-3.163975</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -25594,15 +25520,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Loss (gain) on settlement of accounts</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Loss (gain) on settlement of accounts payable (note 10)</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Loss per share – Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -25648,31 +25578,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N173" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="O173" s="5" t="n">
-        <v>-0.086938</v>
+        <v>-2e-09</v>
       </c>
       <c r="P173" s="5" t="n">
-        <v>0.71889</v>
-      </c>
-      <c r="Q173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.4e-08</v>
+      </c>
+      <c r="Q173" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="R173" s="5" t="n">
+        <v>1e-08</v>
+      </c>
+      <c r="S173" s="5" t="n">
+        <v>1e-08</v>
       </c>
       <c r="T173" t="inlineStr">
         <is>
@@ -25693,12 +25615,12 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Gain on disposal of subsidiary</t>
+          <t>Weighted average outstanding common shares – Basic and</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Gain on disposal of subsidiary company (note 13)</t>
+          <t>Weighted average outstanding common shares – Basic and diluted</t>
         </is>
       </c>
       <c r="D174" t="inlineStr"/>
@@ -25747,33 +25669,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N174" s="5" t="n">
+        <v>140.859109</v>
       </c>
       <c r="O174" s="5" t="n">
-        <v>-0.226991</v>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>151.788479</v>
+      </c>
+      <c r="P174" s="5" t="n">
+        <v>206.411561</v>
+      </c>
+      <c r="Q174" s="5" t="n">
+        <v>263.547976</v>
+      </c>
+      <c r="R174" s="5" t="n">
+        <v>311.783728</v>
+      </c>
+      <c r="S174" s="5" t="n">
+        <v>364.884309</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -25794,17 +25706,17 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the years</t>
+          <t>Consulting fees (note 9)</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -25858,15 +25770,13 @@
         </is>
       </c>
       <c r="O175" s="5" t="n">
-        <v>-0.370889</v>
+        <v>0.411695</v>
       </c>
       <c r="P175" s="5" t="n">
-        <v>-2.977175</v>
-      </c>
-      <c r="Q175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.687481</v>
+      </c>
+      <c r="Q175" s="5" t="n">
+        <v>0.773324</v>
       </c>
       <c r="R175" t="inlineStr">
         <is>
@@ -25897,19 +25807,15 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Loss per share – Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Stock-based compensation (note 10)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -25961,15 +25867,13 @@
         </is>
       </c>
       <c r="O176" s="5" t="n">
-        <v>-2e-09</v>
+        <v>0.043</v>
       </c>
       <c r="P176" s="5" t="n">
-        <v>-1.4e-08</v>
-      </c>
-      <c r="Q176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.753</v>
+      </c>
+      <c r="Q176" s="5" t="n">
+        <v>0.662</v>
       </c>
       <c r="R176" t="inlineStr">
         <is>
@@ -26000,15 +25904,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>common shares – Basic and</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>common shares – Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
+          <t>Foreign exchange loss (gain) (note 3)</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -26060,15 +25968,13 @@
         </is>
       </c>
       <c r="O177" s="5" t="n">
-        <v>151.788479</v>
+        <v>-0.261635</v>
       </c>
       <c r="P177" s="5" t="n">
-        <v>206.411561</v>
-      </c>
-      <c r="Q177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.020592</v>
+      </c>
+      <c r="Q177" s="5" t="n">
+        <v>-0.027415</v>
       </c>
       <c r="R177" t="inlineStr">
         <is>
@@ -26099,19 +26005,15 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Consulting fees (note 8)</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Government assistance benefit (note 8)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -26157,16 +26059,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N178" s="5" t="n">
-        <v>0.45762</v>
-      </c>
-      <c r="O178" s="5" t="n">
-        <v>0.411695</v>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P178" s="5" t="n">
+        <v>-0.017</v>
       </c>
       <c r="Q178" t="inlineStr">
         <is>
@@ -26202,12 +26106,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Dues and fees</t>
+          <t>Loss on settlement of accounts payable (note 10)</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
@@ -26256,16 +26160,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N179" s="5" t="n">
-        <v>0.042864</v>
-      </c>
-      <c r="O179" s="5" t="n">
-        <v>0.070659</v>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P179" s="5" t="n">
+        <v>0.71889</v>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
@@ -26301,19 +26207,15 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Loss (gain) on settlement of accounts</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Foreign exchange gain</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Loss (gain) on settlement of accounts payable (note 10)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -26359,16 +26261,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N180" s="5" t="n">
-        <v>-0.009426</v>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O180" s="5" t="n">
-        <v>-0.261635</v>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.086938</v>
+      </c>
+      <c r="P180" s="5" t="n">
+        <v>0.71889</v>
       </c>
       <c r="Q180" t="inlineStr">
         <is>
@@ -26404,19 +26306,15 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Gain on disposal of subsidiary</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Gain on disposal of subsidiary company (note 13)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr"/>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
@@ -26462,11 +26360,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N181" s="5" t="n">
-        <v>0.06717099999999999</v>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O181" s="5" t="n">
-        <v>0.080651</v>
+        <v>-0.226991</v>
       </c>
       <c r="P181" t="inlineStr">
         <is>
@@ -26507,15 +26407,19 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Office and other</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the years</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E182" t="inlineStr">
         <is>
           <t>-</t>
@@ -26561,16 +26465,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N182" s="5" t="n">
-        <v>0.115855</v>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O182" s="5" t="n">
-        <v>0.079939</v>
-      </c>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.370889</v>
+      </c>
+      <c r="P182" s="5" t="n">
+        <v>-2.977175</v>
       </c>
       <c r="Q182" t="inlineStr">
         <is>
@@ -26606,17 +26510,17 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Net loss and comprehensive loss</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Loss per share – Basic and diluted</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -26664,16 +26568,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N183" s="5" t="n">
-        <v>0.064794</v>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O183" s="5" t="n">
-        <v>0.039086</v>
-      </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-09</v>
+      </c>
+      <c r="P183" s="5" t="n">
+        <v>-1.4e-08</v>
       </c>
       <c r="Q183" t="inlineStr">
         <is>
@@ -26709,19 +26613,15 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>common shares – Basic and</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Shareholder communication</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>common shares – Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr"/>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -26767,16 +26667,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N184" s="5" t="n">
-        <v>0.073105</v>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O184" s="5" t="n">
-        <v>0.07587000000000001</v>
-      </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>151.788479</v>
+      </c>
+      <c r="P184" s="5" t="n">
+        <v>206.411561</v>
       </c>
       <c r="Q184" t="inlineStr">
         <is>
@@ -26817,10 +26717,14 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>Consulting fees (note 8)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -26867,10 +26771,10 @@
         </is>
       </c>
       <c r="N185" s="5" t="n">
-        <v>0.246</v>
+        <v>0.45762</v>
       </c>
       <c r="O185" s="5" t="n">
-        <v>0.043</v>
+        <v>0.411695</v>
       </c>
       <c r="P185" t="inlineStr">
         <is>
@@ -26916,14 +26820,10 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Dues and fees</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -26970,10 +26870,10 @@
         </is>
       </c>
       <c r="N186" s="5" t="n">
-        <v>0.025268</v>
+        <v>0.042864</v>
       </c>
       <c r="O186" s="5" t="n">
-        <v>0.049033</v>
+        <v>0.070659</v>
       </c>
       <c r="P186" t="inlineStr">
         <is>
@@ -27019,10 +26919,14 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Wages and benefits</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
+          <t>Foreign exchange gain</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -27069,10 +26973,10 @@
         </is>
       </c>
       <c r="N187" s="5" t="n">
-        <v>0.13589</v>
+        <v>-0.009426</v>
       </c>
       <c r="O187" s="5" t="n">
-        <v>0.06551999999999999</v>
+        <v>-0.261635</v>
       </c>
       <c r="P187" t="inlineStr">
         <is>
@@ -27118,12 +27022,12 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Expenses total</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -27172,10 +27076,10 @@
         </is>
       </c>
       <c r="N188" s="5" t="n">
-        <v>1.219141</v>
+        <v>0.06717099999999999</v>
       </c>
       <c r="O188" s="5" t="n">
-        <v>0.653818</v>
+        <v>0.080651</v>
       </c>
       <c r="P188" t="inlineStr">
         <is>
@@ -27216,12 +27120,12 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Depreciation expense (note 4)</t>
+          <t>Office and other</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -27270,13 +27174,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N189" s="5" t="n">
+        <v>0.115855</v>
       </c>
       <c r="O189" s="5" t="n">
-        <v>0.031</v>
+        <v>0.079939</v>
       </c>
       <c r="P189" t="inlineStr">
         <is>
@@ -27317,15 +27219,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Gain on settlement of accounts payable (note 8)</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E190" t="inlineStr">
         <is>
           <t>-</t>
@@ -27371,13 +27277,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N190" s="5" t="n">
+        <v>0.064794</v>
       </c>
       <c r="O190" s="5" t="n">
-        <v>-0.086938</v>
+        <v>0.039086</v>
       </c>
       <c r="P190" t="inlineStr">
         <is>
@@ -27418,15 +27322,19 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Other expenses (income)</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Gain on sale of subsidiary company (note 12)</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr"/>
+          <t>Shareholder communication</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -27472,13 +27380,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N191" s="5" t="n">
+        <v>0.073105</v>
       </c>
       <c r="O191" s="5" t="n">
-        <v>-0.226991</v>
+        <v>0.07587000000000001</v>
       </c>
       <c r="P191" t="inlineStr">
         <is>
@@ -27517,10 +27423,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr"/>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>For the years ended March 31, 2019 and March</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -27564,16 +27474,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M192" s="5" t="n">
-        <v>0.002018</v>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N192" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="O192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.246</v>
+      </c>
+      <c r="O192" s="5" t="n">
+        <v>0.043</v>
       </c>
       <c r="P192" t="inlineStr">
         <is>
@@ -27614,12 +27524,12 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Consulting fees (note 8)</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -27662,19 +27572,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L193" s="5" t="n">
-        <v>0.444843</v>
-      </c>
-      <c r="M193" s="5" t="n">
-        <v>0.564095</v>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N193" s="5" t="n">
-        <v>0.45762</v>
-      </c>
-      <c r="O193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025268</v>
+      </c>
+      <c r="O193" s="5" t="n">
+        <v>0.049033</v>
       </c>
       <c r="P193" t="inlineStr">
         <is>
@@ -27715,19 +27627,15 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Wages and benefits</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -27748,28 +27656,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I194" s="5" t="n">
-        <v>0.016504</v>
-      </c>
-      <c r="J194" s="5" t="n">
-        <v>-0.055039</v>
-      </c>
-      <c r="K194" s="5" t="n">
-        <v>0.101065</v>
-      </c>
-      <c r="L194" s="5" t="n">
-        <v>0.021524</v>
-      </c>
-      <c r="M194" s="5" t="n">
-        <v>0.030809</v>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N194" s="5" t="n">
-        <v>-0.009426</v>
-      </c>
-      <c r="O194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.13589</v>
+      </c>
+      <c r="O194" s="5" t="n">
+        <v>0.06551999999999999</v>
       </c>
       <c r="P194" t="inlineStr">
         <is>
@@ -27810,17 +27726,23 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Stock-based compensation</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" s="5" t="n">
-        <v>0.094</v>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -27832,31 +27754,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H195" s="5" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="I195" s="5" t="n">
-        <v>0.306</v>
-      </c>
-      <c r="J195" s="5" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="K195" s="5" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="L195" s="5" t="n">
-        <v>0.4543</v>
-      </c>
-      <c r="M195" s="5" t="n">
-        <v>0.0125</v>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N195" s="5" t="n">
-        <v>0.246</v>
-      </c>
-      <c r="O195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.219141</v>
+      </c>
+      <c r="O195" s="5" t="n">
+        <v>0.653818</v>
       </c>
       <c r="P195" t="inlineStr">
         <is>
@@ -27897,19 +27829,15 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Depreciation expense (note 4)</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -27930,30 +27858,38 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I196" s="5" t="n">
-        <v>0.007735</v>
-      </c>
-      <c r="J196" s="5" t="n">
-        <v>0.008488000000000001</v>
-      </c>
-      <c r="K196" s="5" t="n">
-        <v>0.002246</v>
-      </c>
-      <c r="L196" s="5" t="n">
-        <v>0.01988</v>
-      </c>
-      <c r="M196" s="5" t="n">
-        <v>0.012428</v>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N196" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O196" s="5" t="n">
+        <v>0.031</v>
       </c>
       <c r="P196" t="inlineStr">
         <is>
@@ -27994,19 +27930,15 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the years</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Gain on settlement of accounts payable (note 8)</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -28032,25 +27964,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J197" s="5" t="n">
-        <v>-1.372574</v>
-      </c>
-      <c r="K197" s="5" t="n">
-        <v>-1.833549</v>
-      </c>
-      <c r="L197" s="5" t="n">
-        <v>-10.166843</v>
-      </c>
-      <c r="M197" s="5" t="n">
-        <v>-1.306731</v>
-      </c>
-      <c r="N197" s="5" t="n">
-        <v>-1.219141</v>
-      </c>
-      <c r="O197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O197" s="5" t="n">
+        <v>-0.086938</v>
       </c>
       <c r="P197" t="inlineStr">
         <is>
@@ -28091,19 +28031,15 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Other expenses (income)</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Gain on sale of subsidiary company (note 12)</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
           <t>-</t>
@@ -28119,31 +28055,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H198" s="5" t="n">
-        <v>-4e-08</v>
-      </c>
-      <c r="I198" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="J198" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="K198" s="5" t="n">
-        <v>-3e-08</v>
-      </c>
-      <c r="L198" s="5" t="n">
-        <v>-9e-08</v>
-      </c>
-      <c r="M198" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="N198" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="O198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O198" s="5" t="n">
+        <v>-0.226991</v>
       </c>
       <c r="P198" t="inlineStr">
         <is>
@@ -28182,14 +28130,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
+      <c r="B199" t="inlineStr"/>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Weighted average outstanding common shares – basic and diluted</t>
+          <t>For the years ended March 31, 2019 and March</t>
         </is>
       </c>
       <c r="D199" t="inlineStr"/>
@@ -28208,26 +28152,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H199" s="5" t="n">
-        <v>16.448591</v>
-      </c>
-      <c r="I199" s="5" t="n">
-        <v>36.260226</v>
-      </c>
-      <c r="J199" s="5" t="n">
-        <v>49.235429</v>
-      </c>
-      <c r="K199" s="5" t="n">
-        <v>68.221216</v>
-      </c>
-      <c r="L199" s="5" t="n">
-        <v>116.208746</v>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M199" s="5" t="n">
-        <v>132.296472</v>
+        <v>0.002018</v>
       </c>
       <c r="N199" s="5" t="n">
-        <v>140.859109</v>
+        <v>3.1e-05</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -28271,13 +28225,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B200" t="inlineStr"/>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>For the years ended March 31, 2018 and March</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Consulting fees (note 8)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -28314,15 +28276,13 @@
         </is>
       </c>
       <c r="L200" s="5" t="n">
-        <v>0.002017</v>
+        <v>0.444843</v>
       </c>
       <c r="M200" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.564095</v>
+      </c>
+      <c r="N200" s="5" t="n">
+        <v>0.45762</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -28373,12 +28333,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Interest expense (note 7)</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -28401,33 +28361,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I201" s="5" t="n">
+        <v>0.016504</v>
+      </c>
+      <c r="J201" s="5" t="n">
+        <v>-0.055039</v>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>0.101065</v>
       </c>
       <c r="L201" s="5" t="n">
-        <v>0.07739500000000001</v>
-      </c>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.021524</v>
+      </c>
+      <c r="M201" s="5" t="n">
+        <v>0.030809</v>
+      </c>
+      <c r="N201" s="5" t="n">
+        <v>-0.009426</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -28478,14 +28428,12 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Other fees and penalties</t>
+          <t>Stock-based compensation</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E202" s="5" t="n">
+        <v>0.094</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -28497,38 +28445,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H202" s="5" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="I202" s="5" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="J202" s="5" t="n">
+        <v>0.413</v>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>0.533</v>
       </c>
       <c r="L202" s="5" t="n">
-        <v>0.06560000000000001</v>
-      </c>
-      <c r="M202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.4543</v>
+      </c>
+      <c r="M202" s="5" t="n">
+        <v>0.0125</v>
+      </c>
+      <c r="N202" s="5" t="n">
+        <v>0.246</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -28574,15 +28510,19 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Resource property expenditures (note 5)</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -28603,28 +28543,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I203" s="5" t="n">
+        <v>0.007735</v>
+      </c>
+      <c r="J203" s="5" t="n">
+        <v>0.008488000000000001</v>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>0.002246</v>
       </c>
       <c r="L203" s="5" t="n">
-        <v>0.314855</v>
-      </c>
-      <c r="M203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01988</v>
+      </c>
+      <c r="M203" s="5" t="n">
+        <v>0.012428</v>
       </c>
       <c r="N203" t="inlineStr">
         <is>
@@ -28675,15 +28607,19 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Write-down of mineral properties</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
+          <t>Net loss and comprehensive loss for the years</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -28709,28 +28645,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J204" s="5" t="n">
+        <v>-1.372574</v>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>-1.833549</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>8.131183</v>
-      </c>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-10.166843</v>
+      </c>
+      <c r="M204" s="5" t="n">
+        <v>-1.306731</v>
+      </c>
+      <c r="N204" s="5" t="n">
+        <v>-1.219141</v>
       </c>
       <c r="O204" t="inlineStr">
         <is>
@@ -28774,13 +28702,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr"/>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>For the years ended March 31, 2017 and March</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -28796,36 +28732,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H205" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="I205" s="5" t="n">
+        <v>-5e-08</v>
+      </c>
+      <c r="J205" s="5" t="n">
+        <v>-3e-08</v>
       </c>
       <c r="K205" s="5" t="n">
-        <v>0.002016</v>
+        <v>-3e-08</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-9e-08</v>
+      </c>
+      <c r="M205" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="N205" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="O205" t="inlineStr">
         <is>
@@ -28871,19 +28797,15 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Weighted average outstanding common shares – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -28899,34 +28821,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H206" s="5" t="n">
+        <v>16.448591</v>
+      </c>
+      <c r="I206" s="5" t="n">
+        <v>36.260226</v>
       </c>
       <c r="J206" s="5" t="n">
-        <v>0.3004</v>
+        <v>49.235429</v>
       </c>
       <c r="K206" s="5" t="n">
-        <v>0.427245</v>
+        <v>68.221216</v>
       </c>
       <c r="L206" s="5" t="n">
-        <v>0.444843</v>
-      </c>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>116.208746</v>
+      </c>
+      <c r="M206" s="5" t="n">
+        <v>132.296472</v>
+      </c>
+      <c r="N206" s="5" t="n">
+        <v>140.859109</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
@@ -28970,21 +28884,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B207" t="inlineStr"/>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>For the years ended March 31, 2018 and March</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -29005,24 +28911,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I207" s="5" t="n">
-        <v>0.016504</v>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K207" s="5" t="n">
-        <v>0.101065</v>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L207" s="5" t="n">
-        <v>0.021524</v>
-      </c>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002017</v>
+      </c>
+      <c r="M207" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="N207" t="inlineStr">
         <is>
@@ -29078,7 +28986,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Interest expense (note 7)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -29116,8 +29024,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K208" s="5" t="n">
-        <v>0.051812</v>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L208" s="5" t="n">
         <v>0.07739500000000001</v>
@@ -29181,7 +29091,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Resource property expenditures</t>
+          <t>Other fees and penalties</t>
         </is>
       </c>
       <c r="D209" t="inlineStr"/>
@@ -29221,7 +29131,7 @@
         </is>
       </c>
       <c r="L209" s="5" t="n">
-        <v>0.314855</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="M209" t="inlineStr">
         <is>
@@ -29277,19 +29187,15 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Loss per share – Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Resource property expenditures (note 5)</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>-</t>
@@ -29320,11 +29226,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K210" s="5" t="n">
-        <v>-3e-08</v>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L210" s="5" t="n">
-        <v>-9e-08</v>
+        <v>0.314855</v>
       </c>
       <c r="M210" t="inlineStr">
         <is>
@@ -29380,12 +29288,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Weighted average outstanding common shares – Basic and diluted</t>
+          <t>Write-down of mineral properties</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -29419,11 +29327,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K211" s="5" t="n">
-        <v>68.221216</v>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L211" s="5" t="n">
-        <v>116.208746</v>
+        <v>8.131183</v>
       </c>
       <c r="M211" t="inlineStr">
         <is>
@@ -29480,7 +29390,7 @@
       <c r="B212" t="inlineStr"/>
       <c r="C212" t="inlineStr">
         <is>
-          <t>For the years ended March 31, 2016 and March</t>
+          <t>For the years ended March 31, 2017 and March</t>
         </is>
       </c>
       <c r="D212" t="inlineStr"/>
@@ -29509,16 +29419,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J212" s="5" t="n">
-        <v>0.002015</v>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K212" s="5" t="n">
+        <v>0.002016</v>
+      </c>
+      <c r="L212" s="5" t="n">
         <v>3.1e-05</v>
-      </c>
-      <c r="L212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="M212" t="inlineStr">
         <is>
@@ -29572,13 +29482,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr"/>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>For the years ended March 31, 2015 and March</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -29599,21 +29517,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I213" s="5" t="n">
-        <v>0.002014</v>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J213" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.3004</v>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>0.427245</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>0.444843</v>
       </c>
       <c r="M213" t="inlineStr">
         <is>
@@ -29674,43 +29590,47 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E214" s="5" t="n">
-        <v>0.00013</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G214" s="5" t="n">
-        <v>0.017449</v>
-      </c>
-      <c r="H214" s="5" t="n">
-        <v>0.02423</v>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I214" s="5" t="n">
-        <v>0.027956</v>
-      </c>
-      <c r="J214" s="5" t="n">
-        <v>0.035258</v>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.016504</v>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>0.101065</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>0.021524</v>
       </c>
       <c r="M214" t="inlineStr">
         <is>
@@ -29771,10 +29691,14 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Write-down of resource properties</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr"/>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -29785,31 +29709,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G215" s="5" t="n">
-        <v>0.19</v>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I215" s="5" t="n">
-        <v>0.9180160000000001</v>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K215" s="5" t="n">
+        <v>0.051812</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>0.07739500000000001</v>
       </c>
       <c r="M215" t="inlineStr">
         <is>
@@ -29865,19 +29789,15 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Resource property expenditures</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr"/>
       <c r="E216" t="inlineStr">
         <is>
           <t>-</t>
@@ -29893,24 +29813,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H216" s="5" t="n">
-        <v>-0.599882</v>
-      </c>
-      <c r="I216" s="5" t="n">
-        <v>-1.910207</v>
-      </c>
-      <c r="J216" s="5" t="n">
-        <v>-1.372574</v>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L216" s="5" t="n">
+        <v>0.314855</v>
       </c>
       <c r="M216" t="inlineStr">
         <is>
@@ -29964,13 +29888,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr"/>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>For the years ended March 31, 2014 and March</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
+          <t>Loss per share – Basic and diluted</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -29986,26 +29918,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H217" s="5" t="n">
-        <v>0.002013</v>
-      </c>
-      <c r="I217" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K217" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>-9e-08</v>
       </c>
       <c r="M217" t="inlineStr">
         <is>
@@ -30061,28 +29993,34 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Property investigation</t>
+          <t>Weighted average outstanding common shares – Basic and diluted</t>
         </is>
       </c>
       <c r="D218" t="inlineStr"/>
-      <c r="E218" s="5" t="n">
-        <v>0.00508</v>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G218" s="5" t="n">
-        <v>0.07333199999999999</v>
-      </c>
-      <c r="H218" s="5" t="n">
-        <v>0.108647</v>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
@@ -30094,15 +30032,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K218" s="5" t="n">
+        <v>68.221216</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>116.208746</v>
       </c>
       <c r="M218" t="inlineStr">
         <is>
@@ -30156,21 +30090,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
+      <c r="B219" t="inlineStr"/>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>For the years ended March 31, 2016 and March</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -30186,21 +30112,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H219" s="5" t="n">
-        <v>-0.640882</v>
-      </c>
-      <c r="I219" s="5" t="n">
-        <v>-1.910207</v>
-      </c>
-      <c r="J219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J219" s="5" t="n">
+        <v>0.002015</v>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="L219" t="inlineStr">
         <is>
@@ -30259,21 +30185,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Other income</t>
-        </is>
-      </c>
+      <c r="B220" t="inlineStr"/>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Recovery of income taxes</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
+          <t>For the years ended March 31, 2015 and March</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr"/>
       <c r="E220" t="inlineStr">
         <is>
           <t>-</t>
@@ -30289,18 +30207,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H220" s="5" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="I220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I220" s="5" t="n">
+        <v>0.002014</v>
+      </c>
+      <c r="J220" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -30364,17 +30280,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B221" t="inlineStr"/>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>For the years ended March 31, 2013 and March</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Office</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E221" s="5" t="n">
+        <v>0.00013</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -30382,20 +30304,16 @@
         </is>
       </c>
       <c r="G221" s="5" t="n">
-        <v>0.002012</v>
+        <v>0.017449</v>
       </c>
       <c r="H221" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="I221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.02423</v>
+      </c>
+      <c r="I221" s="5" t="n">
+        <v>0.027956</v>
+      </c>
+      <c r="J221" s="5" t="n">
+        <v>0.035258</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -30466,16 +30384,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Loss before income taxes</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
-      <c r="E222" s="5" t="n">
-        <v>-0.154853</v>
+          <t>Write-down of resource properties</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -30483,15 +30399,15 @@
         </is>
       </c>
       <c r="G222" s="5" t="n">
-        <v>-0.631835</v>
-      </c>
-      <c r="H222" s="5" t="n">
-        <v>-0.640882</v>
-      </c>
-      <c r="I222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.19</v>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I222" s="5" t="n">
+        <v>0.9180160000000001</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -30562,17 +30478,17 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Recovery of income taxes</t>
+          <t>Net loss and comprehensive loss for the year</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -30585,21 +30501,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G223" s="5" t="n">
-        <v>0.0315</v>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H223" s="5" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="I223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.599882</v>
+      </c>
+      <c r="I223" s="5" t="n">
+        <v>-1.910207</v>
+      </c>
+      <c r="J223" s="5" t="n">
+        <v>-1.372574</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -30663,39 +30577,33 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
+      <c r="B224" t="inlineStr"/>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Net loss and comprehensive loss for the year</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E224" s="5" t="n">
-        <v>-0.154853</v>
+          <t>For the years ended March 31, 2014 and March</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G224" s="5" t="n">
-        <v>-0.600335</v>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H224" s="5" t="n">
-        <v>-0.599882</v>
-      </c>
-      <c r="I224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002013</v>
+      </c>
+      <c r="I224" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -30771,16 +30679,12 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Property investigation</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr"/>
       <c r="E225" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.00508</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -30788,10 +30692,10 @@
         </is>
       </c>
       <c r="G225" s="5" t="n">
-        <v>-7e-08</v>
+        <v>0.07333199999999999</v>
       </c>
       <c r="H225" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.108647</v>
       </c>
       <c r="I225" t="inlineStr">
         <is>
@@ -30867,90 +30771,1102 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H226" s="5" t="n">
+        <v>-0.640882</v>
+      </c>
+      <c r="I226" s="5" t="n">
+        <v>-1.910207</v>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Recovery of income taxes</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H227" s="5" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>For the years ended March 31, 2013 and March</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G228" s="5" t="n">
+        <v>0.002012</v>
+      </c>
+      <c r="H228" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
           <t>Operating expenses</t>
         </is>
       </c>
-      <c r="C226" t="inlineStr">
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Loss before income taxes</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
+      <c r="E229" s="5" t="n">
+        <v>-0.154853</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G229" s="5" t="n">
+        <v>-0.631835</v>
+      </c>
+      <c r="H229" s="5" t="n">
+        <v>-0.640882</v>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Recovery of income taxes</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G230" s="5" t="n">
+        <v>0.0315</v>
+      </c>
+      <c r="H230" s="5" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the year</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E231" s="5" t="n">
+        <v>-0.154853</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G231" s="5" t="n">
+        <v>-0.600335</v>
+      </c>
+      <c r="H231" s="5" t="n">
+        <v>-0.599882</v>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E232" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="F232" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="G232" s="5" t="n">
+        <v>-7e-08</v>
+      </c>
+      <c r="H232" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
         <is>
           <t>Weighted average outstanding common shares – basic and diluted</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" s="5" t="n">
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" s="5" t="n">
         <v>3.908902</v>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G226" s="5" t="n">
+      <c r="F233" s="5" t="n">
+        <v>7.399313</v>
+      </c>
+      <c r="G233" s="5" t="n">
         <v>9.091049999999999</v>
       </c>
-      <c r="H226" s="5" t="n">
+      <c r="H233" s="5" t="n">
         <v>16.448591</v>
       </c>
-      <c r="I226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="T226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="U226" t="inlineStr">
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" s="5" t="n">
+        <v>0.019877</v>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Stock-based compensation expenses</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Net loss and comprehensive loss for the period and Deficit – End of period</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F236" s="5" t="n">
+        <v>-0.154853</v>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
         <is>
           <t>-</t>
         </is>
